--- a/data_extactor/batch_10_fa/trimmed/batch_0052_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0052_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن</t>
+          <t>گوش دادن فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی</t>
+          <t>خدمات مشتری و شخصی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | استحکام بالاتنه | تشخیص گفتار | حساسیت به مسئله | استحکام استاتیک | بیان شفاهی | چابکی دستی</t>
+          <t>درک شفاهی | قدرت تنه | تشخیص گفتار | حساسیت به مسئله | قدرت ایستا | بیان شفاهی | مهارت دستی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>رانندگان و خدمه آمبولانس، به جز تکنسین‌های فوریت‌های پزشکی | تکنسین‌های فوریت‌های پزشکی (EMT) | مراقبان سلامت در منزل | متصدیان آماده‌سازی و استریل تجهیزات پزشکی | کمک‌بهیاران | مراقبان مراقبت‌های فردی | تکنسین‌های اتاق عمل</t>
+          <t>رانندگان و خدمه آمبولانس، به‌جز تکنسین‌های فوریت‌های پزشکی | تکنسین‌های فوریت‌های پزشکی | مراقبان سلامت و بهیاران مراقبت در منزل | متصدیان آماده‌سازی و استریل تجهیزات پزشکی | کمک‌پرستاران | مراقبان خدمات شخصی و همراهان توان‌خواهان | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | نظارت | تفکر انتقادی | یادگیری فعال | درک مطلب | نگارش</t>
+          <t>سخن گفتن | گوش دادن فعال | نظارت | تفکر انتقادی | یادگیری فعال | درک مطلب | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>روان‌شناسی | خدمات مشتریان و خدمات فردی | درمان و مشاوره | زبان انگلیسی</t>
+          <t>روان‌شناسی | خدمات مشتری و شخصی | درمان و مشاوره | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | درک کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | درک کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>پرستاران تخصصی سلامت روان | مراقبان سلامت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | مشاوران سلامت روان | کمک‌بهیاران | تکنسین‌های روان‌پزشکی | کارشناسان پرستاری</t>
+          <t>پرستاران تخصصی روانپزشکی | مراقبان سلامت و بهیاران مراقبت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | مشاوران سلامت روان | کمک‌پرستاران | تکنسین‌های روان‌پزشکی و بهداشت روان | پرستاران</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نظارت | تفکر انتقادی | نگارش | راهبردهای یادگیری | یادگیری فعال</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نظارت | تفکر انتقادی | نگارش | راهبردهای یادگیری | یادگیری فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | روان‌شناسی | آموزش و تدریس | درمان و مشاوره | ایمنی و امنیت عمومی | پزشکی و دندان‌پزشکی</t>
+          <t>خدمات مشتری و شخصی | روان‌شناسی | آموزش و پرورش | درمان و مشاوره | ایمنی و امنیت عمومی | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | درک کتبی | دید نزدیک | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | درک کتبی | بینایی نزدیک | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>بهیاران و کمک‌پرستاران دارای مجوز | ماساژدرمانگران | کارشناسان کاردرمانی | کمک‌یاران کاردرمانی | متخصصان طب فیزیکی و توانبخشی | کاردانی‌های فیزیوتراپی | کارشناسان فیزیوتراپی</t>
+          <t>بهیاران و کمک‌پرستاران دارای مجوز | ماساژدرمانگران | کاردرمانگران | کمک‌یاران کاردرمانی | متخصصان طب فیزیکی و توانبخشی | کاردان‌های فیزیوتراپی | فیزیوتراپیست‌ها</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | تفکر انتقادی | نظارت | درک مطلب | نگارش | راهبردهای یادگیری | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | نظارت | درک مطلب | نگارش | راهبردهای یادگیری | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | خدمات مشتریان و خدمات فردی | روان‌شناسی | آموزش و تدریس | پزشکی و دندان‌پزشکی | ایمنی و امنیت عمومی</t>
+          <t>درمان و مشاوره | خدمات مشتری و شخصی | روان‌شناسی | آموزش و پرورش | پزشکی و دندان‌پزشکی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | استدلال قیاسی | وضوح گفتار | مرتب‌سازی اطلاعات | دید نزدیک</t>
+          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | استدلال قیاسی | وضوح گفتار | ترتیب‌دهی اطلاعات | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مراقبان سلامت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | کمک‌بهیاران | کارشناسان کاردرمانی | کاردانی‌های کاردرمانی | کمک‌یاران فیزیوتراپی | کاردانی‌های فیزیوتراپی</t>
+          <t>مراقبان سلامت و بهیاران مراقبت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | کمک‌پرستاران | کاردرمانگران | کاردان‌های کاردرمانی | کمک‌یاران فیزیوتراپی | کاردان‌های فیزیوتراپی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت | یادگیری فعال | تفکر انتقادی | نگارش | درک مطلب</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | یادگیری فعال | تفکر انتقادی | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | درمان و مشاوره | آموزش و تدریس | روان‌شناسی | پزشکی و دندان‌پزشکی | زیست‌شناسی</t>
+          <t>خدمات مشتری و شخصی | درمان و مشاوره | آموزش و پرورش | روان‌شناسی | پزشکی و دندان‌پزشکی | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | درک کتبی | حساسیت به مسئله | دید نزدیک | ثبات دست و بازو</t>
+          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | درک کتبی | حساسیت به مسئله | بینایی نزدیک | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>بهیاران و کمک‌پرستاران دارای مجوز | ماساژدرمانگران | کارشناسان کاردرمانی | متخصصان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | کارشناسان فیزیوتراپی | کارشناسان تفریح‌درمانی</t>
+          <t>بهیاران و کمک‌پرستاران دارای مجوز | ماساژدرمانگران | کاردرمانگران | متخصصان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | فیزیوتراپیست‌ها | کارشناسان تفریح‌درمانی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | درک مطلب | یادگیری فعال | تفکر انتقادی | سخن گفتن | نگارش</t>
+          <t>گوش دادن فعال | نظارت | درک مطلب | یادگیری فعال | تفکر انتقادی | سخن گفتن | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | رایانه و الکترونیک | درمان و مشاوره</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | رایانه و الکترونیک | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | تشخیص گفتار | دید نزدیک | بیان شفاهی | درک کتبی | استحکام بالاتنه</t>
+          <t>درک شفاهی | حساسیت به مسئله | تشخیص گفتار | بینایی نزدیک | بیان شفاهی | درک کتبی | قدرت تنه</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مراقبان سلامت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | ماساژدرمانگران | کمک‌یاران کاردرمانی | متخصصان طب فیزیکی و توانبخشی | کاردانی‌های فیزیوتراپی | کارشناسان فیزیوتراپی</t>
+          <t>مراقبان سلامت و بهیاران مراقبت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | ماساژدرمانگران | کمک‌یاران کاردرمانی | متخصصان طب فیزیکی و توانبخشی | کاردان‌های فیزیوتراپی | فیزیوتراپیست‌ها</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,22 +845,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AppointmentQuest Online Appointment Manager | ICS Software SammyUSA | Land Software Customer Pro-File | Massage Suite | Microsoft Excel | Microsoft Word | نرم‌افزار نوبت‌دهی | WinCity Custom Software WinCity Massage SOAP Notes</t>
+          <t>AppointmentQuest Online Appointment Manager | ICS Software SammyUSA | Land Software Customer Pro-File | Massage Suite | Microsoft Excel | Microsoft Word | نرم‌افزار زمان‌بندی | WinCity Custom Software WinCity Massage SOAP Notes</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت | یادگیری فعال | تفکر انتقادی | نگارش | درک مطلب</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | یادگیری فعال | تفکر انتقادی | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زیست‌شناسی | زبان انگلیسی | روان‌شناسی | پزشکی و دندان‌پزشکی | ایمنی و امنیت عمومی | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | زیست‌شناسی | زبان انگلیسی | روان‌شناسی | پزشکی و دندان‌پزشکی | ایمنی و امنیت عمومی | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>قدرت دینامیک | استحکام بالاتنه | درک شفاهی | بیان شفاهی | چابکی دستی | هماهنگی چندعضوی | حساسیت به مسئله</t>
+          <t>قدرت پویا | قدرت تنه | درک شفاهی | بیان شفاهی | مهارت دستی | هماهنگی چند عضو | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>متخصصان طب سوزنی | کایروپراکتورها | کارشناسان کاردرمانی | متخصصان طب فیزیکی و توانبخشی | کاردانی‌های فیزیوتراپی | کارشناسان فیزیوتراپی | متخصصان مراقبت از پوست</t>
+          <t>متخصصان و کارشناسان طب سوزنی | کایروپراکتورها / متخصصان درمان دستی | کاردرمانگران | متخصصان طب فیزیکی و توانبخشی | کاردان‌های فیزیوتراپی | فیزیوتراپیست‌ها | متخصصان و تکنسین‌های مراقبت از پوست</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | یادگیری فعال | نظارت | تفکر انتقادی | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | یادگیری فعال | نظارت | تفکر انتقادی | نگارش</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | پزشکی و دندان‌پزشکی | مدیریت و امور اداری | اداری و سازمانی | رایانه و الکترونیک | تولید و فرآوری</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | مدیریت و اداره | اداری | رایانه و الکترونیک | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | بیان شفاهی | درک شفاهی | درک کتبی | استدلال قیاسی | مرتب‌سازی اطلاعات | چابکی انگشتان</t>
+          <t>بینایی نزدیک | بیان شفاهی | درک شفاهی | درک کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>کارشناسان بهداشت دهان و دندان | دندانسازان (تکنسین‌های پروتز دندانی) | دندان‌پزشکان عمومی | دستیاران پزشک | جراحان دهان، فک و صورت | متخصصان ارتودنسی | متخصصان پروتزهای دندانی</t>
+          <t>بهداشت‌کاران دهان و دندان | تکنسین‌های پروتزهای دندانی و لابراتوار دندانسازی | دندان‌پزشکان عمومی | کمک‌پزشکان و دستیاران مطب | جراحان دهان، فک و صورت | متخصصان ارتودنسی | متخصصان پروتزهای دندانی (پروستودنتیست‌ها)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>دستیاران پزشک (Medical Assistants)</t>
+          <t>کمک‌پزشکان و دستیاران مطب (Medical Assistants)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | پزشکی و دندان‌پزشکی | اداری و سازمانی | رایانه و الکترونیک | آموزش و تدریس | ایمنی و امنیت عمومی</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | اداری | رایانه و الکترونیک | آموزش و پرورش | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | دید نزدیک | بیان کتبی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | بینایی نزدیک | بیان کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>دستیاران دندان‌پزشک | پزشکان عمومی و خانواده | بهیاران و کمک‌پرستاران دارای مجوز | متصدیان اسناد و مدارک پزشکی | کمک‌بهیاران | تکنسین‌های پیش‌بیمارستانی (پارامدیک) | کارشناسان پرستاری</t>
+          <t>دستیاران دندان‌پزشک | پزشکان عمومی و خانواده | بهیاران و کمک‌پرستاران دارای مجوز | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | کمک‌پرستاران | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | پرستاران</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | شنیدن فعال | درک مطلب | سخن گفتن | یادگیری فعال</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال | درک مطلب | سخن گفتن | یادگیری فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | زیست‌شناسی | تولید و فرآوری | ایمنی و امنیت عمومی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | زیست‌شناسی | تولید و فرآوری | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>دید نزدیک | حساسیت به مسئله | درک شفاهی | چابکی دستی | چابکی انگشتان | بیان شفاهی | مرتب‌سازی اطلاعات</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | درک شفاهی | مهارت دستی | مهارت انگشتان | بیان شفاهی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان کالیبراسیون | تکنسین‌های فوریت‌های پزشکی (EMT) | تکنسین‌های آندوسکوپی | تعمیرکاران تجهیزات پزشکی | تکنسین‌های آزمایشگاه پزشکی و بالینی | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
+          <t>تکنسین‌ها و کارشناسان فنی کالیبراسیون | تکنسین‌های فوریت‌های پزشکی | تکنسین‌های اندوسکوپی | تعمیرکاران تجهیزات پزشکی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
